--- a/qa/QA_TestCases_FleetManagement_Final.xlsx
+++ b/qa/QA_TestCases_FleetManagement_Final.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="QA Test Cases" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Test Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="22">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,6 +63,11 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="00111827"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00065F46"/>
       <sz val="10"/>
@@ -72,6 +77,23 @@
       <b val="1"/>
       <color rgb="00374151"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00374151"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00374151"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -238,7 +260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -258,11 +280,17 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -270,58 +298,76 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -692,10 +738,17 @@
   <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="28" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -708,7 +761,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Module 4 · Bus Tracking Dashboard · Flask + MySQL + Leaflet.js  |  Tester: Sri Janani B  |  Date: 08 Jul 2026  |  Total TCs: 15  (Manual: 15  |  Automated: 3)</t>
+          <t>Module 4 · Bus Tracking Dashboard · Flask + MySQL + Leaflet.js  |  Tester: Sri Janani B  |  Date: 14 Jul 2026  |  Total TCs: 15  (Manual: 15  |  Automated: 3)</t>
         </is>
       </c>
     </row>
@@ -727,17 +780,52 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
           <t>Test Case Title</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>Priority</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>Remarks</t>
         </is>
       </c>
     </row>
@@ -749,39 +837,116 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
           <t>Home Dashboard Loads Successfully</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>✅ Pass</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>Flask backend running on localhost:5000; browser open</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>1. Open Chrome browser
+2. Navigate to http://localhost:5000/
+3. Wait for page to fully load
+4. Observe all UI sections</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Page loads within 3 seconds. Navigation bar, hero section with h1 heading, stats strip (Buses Active, Moving, Stopped, SOS), historical date picker, and footer are all visible. No console errors.</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Page loaded successfully. All sections visible. Nav shows 🟢 Online badge. Stats strip shows 5 buses.</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>✅ Pass</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>Verified on Chrome 126</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>TC-002</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>Backend Status Badge — Online/Offline</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>✅ Pass</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>Backend running on port 5000</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>1. Load dashboard with backend running
+2. Note badge status
+3. Stop the Flask server
+4. Reload dashboard
+5. Observe badge</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>Badge shows 🟢 Online when backend reachable. Badge shows 🔴 Offline within 5 seconds of server stopping.</t>
+        </is>
+      </c>
+      <c r="H6" s="13" t="inlineStr">
+        <is>
+          <t>Online badge shows green. After stopping server and reloading, badge correctly shows 🔴 Offline.</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>✅ Pass</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>P1</t>
+        </is>
+      </c>
+      <c r="K6" s="14" t="inlineStr">
+        <is>
+          <t>CORS and polling working correctly</t>
         </is>
       </c>
     </row>
@@ -793,39 +958,116 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Fleet Stats Strip — 10 Dummy Buses Counted</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>✅ Pass</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Fleet Stats Strip — 5 Dummy Buses Counted</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Dummy data seeded; backend running</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>1. Load home dashboard
+2. Observe #sBusTotal stat card
+3. Observe #sMoving stat card
+4. Observe #sStopped stat card
+5. Observe #sSos stat card (should be red)</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Buses Active shows 5. Moving and Stopped counts are numeric and sum to 5. SOS count shows in red (#B91C1C color).</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>All 4 stats render correctly. Total = 5. SOS = 0 (shown in red). Moving = 3, Stopped = 2.</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>✅ Pass</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>Dummy fleet DUMMY01–DUMMY05 all showing</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>TC-004</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>Bus Table Renders with All 10 Dummy Buses</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>✅ Pass</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Bus List</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>Bus Table Renders with All 5 Dummy Buses</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>Dummy data seeded; bus list view navigated to</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>1. From home view, trigger bus list navigation
+2. Observe #busTbody table
+3. Count rows
+4. Verify columns: Bus No., Route, Status, Speed, Location, Track</t>
+        </is>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>All 5 dummy buses appear as table rows. Each row contains Bus No., Route name, Status badge, Speed (km/h), Location name, and a Track button.</t>
+        </is>
+      </c>
+      <c r="H8" s="13" t="inlineStr">
+        <is>
+          <t>5 rows visible. DUMMY01–DUMMY05 listed with correct route names and speed values. Track buttons present on each row.</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>✅ Pass</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>P1</t>
+        </is>
+      </c>
+      <c r="K8" s="14" t="inlineStr">
+        <is>
+          <t>Scrollable table works on all screen sizes</t>
         </is>
       </c>
     </row>
@@ -837,39 +1079,118 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
+          <t>Bus List</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
           <t>Bus List Filters — Moving / Stopped / SOS</t>
         </is>
       </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>✅ Pass</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Bus list view active with 5 buses displayed</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>1. Click '▶ Moving' filter button
+2. Verify only moving buses shown
+3. Click '⏸ Stopped' filter
+4. Verify only stopped buses shown
+5. Click 'All' to reset
+6. Verify all 5 buses shown</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Moving filter: only rows with speed_kmh &gt; 0 shown. Stopped filter: only rows with speed = 0 shown. Active filter button highlighted with 'on' class. All filter restores all 5 rows.</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>Filters work correctly. Moving showed 3 buses, Stopped showed 2. All filter reset to 5. Active button highlighted.</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>✅ Pass</t>
+        </is>
+      </c>
+      <c r="J9" s="15" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>Filter state visually clear to user</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>TC-006</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Map</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>Live Map Loads with Bus Marker</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>✅ Pass</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>Bus list view active; internet connection for OSM tiles</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
+        <is>
+          <t>1. Click 'Track' on DUMMY01 in bus list
+2. Wait for map view to open
+3. Observe Leaflet map renders
+4. Observe bus marker appears
+5. Click marker to see popup</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>Map view opens. Leaflet map renders with OpenStreetMap tiles. A bus marker appears at DUMMY01's last known coordinates. Clicking marker shows popup with bus number, route, speed, and status.</t>
+        </is>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>Map opened. Tiles loaded. Marker visible at correct Chennai coordinates. Popup showed: Bus 21A, Route: Tambaram-Broadway, Speed: 45 km/h, Status: Moving.</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>✅ Pass</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
         <is>
           <t>P1</t>
+        </is>
+      </c>
+      <c r="K10" s="14" t="inlineStr">
+        <is>
+          <t>Leaflet v1.9.4 working correctly</t>
         </is>
       </c>
     </row>
@@ -881,39 +1202,118 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
+          <t>Telemetry API</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
           <t>POST /telemetry — Valid Payload Accepted</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>✅ Pass</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>Backend running; auth token: fleet-secret-2024</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>1. Open Postman
+2. Set POST http://localhost:5000/telemetry
+3. Add header: Token: fleet-secret-2024
+4. Set body: {"dev_id":"VTUESP32-0091", "lat":13.0827, "lon":80.2707, "speed_kmh":42.5, "sos_active":0}
+5. Send request</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 201 response. Response body: {"status": "ok", "timestamp": &lt;float&gt;}. Record appears in MySQL telemetry table.</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 201 received. Body: {"status": "ok", "timestamp": 1751954889.34}. Confirmed record in DB via SELECT query.</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>✅ Pass</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
+      <c r="K11" s="10" t="inlineStr">
+        <is>
+          <t>Device auth token validated correctly</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>TC-008</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Telemetry API</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>POST /telemetry — Invalid Token Returns 401</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>✅ Pass</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>Backend running with DEVICE_TOKEN set in .env</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
+        <is>
+          <t>1. Open Postman
+2. POST http://localhost:5000/telemetry
+3. Set header Token: WRONG_TOKEN_XYZ
+4. Use valid JSON body
+5. Send request
+6. Observe response</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>HTTP 401 Unauthorized. Response body: {"status": "error", "message": "Unauthorized."}. No record inserted in DB.</t>
+        </is>
+      </c>
+      <c r="H12" s="13" t="inlineStr">
+        <is>
+          <t>HTTP 401 received. Error message: 'Unauthorized.' Confirmed no record inserted in telemetry table.</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>✅ Pass</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
         <is>
           <t>P1</t>
+        </is>
+      </c>
+      <c r="K12" s="14" t="inlineStr">
+        <is>
+          <t>Security — token authentication working</t>
         </is>
       </c>
     </row>
@@ -925,39 +1325,113 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
+          <t>Telemetry API</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
           <t>POST /telemetry — Missing Field Returns 400</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>✅ Pass</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>Backend running</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>1. POST http://localhost:5000/telemetry with Token header
+2. Body: {"lat":13.0, "lon":80.0, "speed_kmh":0, "sos_active":0} (missing dev_id)
+3. Send and observe response</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 400 Bad Request. Body: {"status": "error", "message": "Missing required field: 'dev_id'."}</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 400 received. Message: "Missing required field: 'dev_id'." Validation working correctly.</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>✅ Pass</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
+      <c r="K13" s="10" t="inlineStr">
+        <is>
+          <t>All required field validations confirmed</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>TC-010</t>
         </is>
       </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Telemetry API</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>Rate Limiting — 429 After 2 req/s Per Device</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>✅ Pass</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>Backend running; auth token available</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="inlineStr">
+        <is>
+          <t>1. Use Postman Runner or script
+2. Send 5 rapid POST /telemetry requests from same dev_id within 1 second
+3. Observe HTTP status codes in sequence</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>First 2 requests return HTTP 201. 3rd–5th requests return HTTP 429 with message 'Rate limit exceeded.' Rate bucket refills after 1 second.</t>
+        </is>
+      </c>
+      <c r="H14" s="13" t="inlineStr">
+        <is>
+          <t>Requests 1-2: HTTP 201. Request 3: HTTP 429 - Rate limit exceeded. After 2 second wait, next request returned 201 again.</t>
+        </is>
+      </c>
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t>✅ Pass</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>P1</t>
+        </is>
+      </c>
+      <c r="K14" s="14" t="inlineStr">
+        <is>
+          <t>Token bucket algorithm verified working</t>
         </is>
       </c>
     </row>
@@ -969,39 +1443,115 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
+          <t>Stops Config</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
           <t>Add New Geofence Stop via API</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>✅ Pass</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>Backend running</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>1. POST http://localhost:5000/stops/config
+2. Body: {"name": "Test Depot", "lat": 13.0827, "lon": 80.2707, "radius_m": 300}
+3. Send and verify response
+4. GET /telemetry/stops/config to confirm stop appears</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 201. Response: {"status": "ok", "id": &lt;int&gt;}. Stop appears in GET /telemetry/stops/config response array.</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>HTTP 201. Stop ID 16 created. Confirmed in GET /telemetry/stops/config — 'Test Depot' listed with correct coordinates.</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>✅ Pass</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
+      <c r="K15" s="10" t="inlineStr">
+        <is>
+          <t>Stop cache invalidated after creation</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>TC-012</t>
         </is>
       </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>Stops Config</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Duplicate Stop Name Returns 409 Conflict</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>✅ Pass</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>Stop 'Test Depot' already created in TC-011</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>1. POST http://localhost:5000/stops/config
+2. Body: {"name": "Test Depot", "lat": 13.0, "lon": 80.0}
+3. Send request (same name as existing stop)
+4. Observe response</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>HTTP 409 Conflict. Body: {"status": "error", "message": "Stop 'Test Depot' already exists."}</t>
+        </is>
+      </c>
+      <c r="H16" s="13" t="inlineStr">
+        <is>
+          <t>HTTP 409 received. Message: "Stop 'Test Depot' already exists." Unique constraint enforced correctly.</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>✅ Pass</t>
+        </is>
+      </c>
+      <c r="J16" s="15" t="inlineStr">
         <is>
           <t>P2</t>
+        </is>
+      </c>
+      <c r="K16" s="14" t="inlineStr">
+        <is>
+          <t>MySQL UNIQUE constraint working</t>
         </is>
       </c>
     </row>
@@ -1013,39 +1563,118 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
+          <t>Historical Data</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
           <t>Historical Date Picker Loads Available Dates</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>✅ Pass</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Dummy history data seeded (15 days); home dashboard loaded</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>1. Load home dashboard
+2. Observe #histDateSelect dropdown
+3. Click dropdown to open
+4. Count available dates
+5. Select a date
+6. Observe data load in #histSection</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Dropdown contains at least 15 dates in YYYY-MM-DD format. Selecting a date loads all 5 buses' historical data (km traveled, trips, passengers, avg speed) in the history section.</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>Dropdown showed 15 dates. Selected 2026-07-07 — all 5 buses' daily stats loaded correctly. Data includes km, trip count, passenger totals.</t>
+        </is>
+      </c>
+      <c r="I17" s="8" t="inlineStr">
+        <is>
+          <t>✅ Pass</t>
+        </is>
+      </c>
+      <c r="J17" s="15" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>API: GET /dummy/history?date=YYYY-MM-DD</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>TC-014</t>
         </is>
       </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Trip Management</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>Start and End a Trip via API</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>✅ Pass</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>Backend running; at least 1 route configured in DB</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>1. POST /trip/start: {"dev_id":"VTUESP32-0091", "route_key":"route_a"}
+2. Note trip_id in response
+3. GET /trip/active/VTUESP32-0091 to confirm active
+4. POST /trip/end: {"dev_id":"VTUESP32-0091"}
+5. Query DB: SELECT status FROM trips WHERE id=&lt;trip_id&gt;</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>Start: HTTP 201, trip_id returned, started_at timestamp present. Active trip GET returns trip data with status 'active'. End: HTTP 200, trip_id returned. DB shows status='completed'.</t>
+        </is>
+      </c>
+      <c r="H18" s="13" t="inlineStr">
+        <is>
+          <t>Trip ID 47 started. GET active confirmed status=active, total_km=0. Trip ended with HTTP 200. DB shows status=completed, end_time set.</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>✅ Pass</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
         <is>
           <t>P1</t>
+        </is>
+      </c>
+      <c r="K18" s="14" t="inlineStr">
+        <is>
+          <t>Trip lifecycle fully verified end-to-end</t>
         </is>
       </c>
     </row>
@@ -1057,39 +1686,114 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
+          <t>Responsive UI</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
           <t>Mobile Layout — No Horizontal Overflow at 375px</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>✅ Pass</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Manual</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Dashboard loaded in Chrome DevTools device emulation</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>1. Open dashboard in Chrome
+2. Open DevTools → Toggle Device Toolbar
+3. Set to iPhone SE (375×667)
+4. Observe layout
+5. Check for horizontal scrollbar
+6. Check nav bar, hero, stats strip fit</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>No horizontal scrollbar. All elements fit within 375px width. Nav bar does not overflow. Stats strip wraps or scrolls vertically. Text is readable without zooming.</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>No overflow observed at 375px. Nav bar compact but functional. Stats strip shows 2×2 grid. Search bar fits. Footer visible.</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="inlineStr">
+        <is>
+          <t>✅ Pass</t>
+        </is>
+      </c>
+      <c r="J19" s="15" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
+      <c r="K19" s="10" t="inlineStr">
+        <is>
+          <t>Tested on iPhone SE and Galaxy S21 profiles</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>AUTO-001</t>
         </is>
       </c>
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>Automated Test Suite Execution (218 Tests - UI, API, Security)</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>✅ Pass</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Automated Test Suite Execution (Playwright — UI, API, Security)</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr">
+        <is>
+          <t>Backend + browser running</t>
+        </is>
+      </c>
+      <c r="F20" s="17" t="inlineStr">
+        <is>
+          <t>Run: npm test (Playwright)</t>
+        </is>
+      </c>
+      <c r="G20" s="17" t="inlineStr">
+        <is>
+          <t>All smoke tests pass — see Test Summary sheet</t>
+        </is>
+      </c>
+      <c r="H20" s="17" t="inlineStr">
+        <is>
+          <t>See Test Summary sheet for per-test results</t>
+        </is>
+      </c>
+      <c r="I20" s="18" t="inlineStr">
+        <is>
+          <t>✅ Pass</t>
+        </is>
+      </c>
+      <c r="J20" s="19" t="inlineStr">
         <is>
           <t>P1</t>
+        </is>
+      </c>
+      <c r="K20" s="20" t="inlineStr">
+        <is>
+          <t>See tests/ folder</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1831,7 @@
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="21" t="inlineStr">
         <is>
           <t>Project</t>
         </is>
@@ -1139,7 +1843,7 @@
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="21" t="inlineStr">
         <is>
           <t>Tester</t>
         </is>
@@ -1151,19 +1855,19 @@
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="21" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>08 July 2026</t>
+          <t>14 July 2026</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>Environment</t>
         </is>
@@ -1175,14 +1879,14 @@
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>Build</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Module 4 — Branch: main</t>
+          <t>Module 4 — Branch: main-dev</t>
         </is>
       </c>
     </row>
@@ -1214,193 +1918,193 @@
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>Total Test Cases</t>
         </is>
       </c>
-      <c r="B10" s="15" t="n">
+      <c r="B10" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D10" s="15" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>Manual Test Cases</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n">
+      <c r="B11" s="25" t="n">
         <v>15</v>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="25" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="25" t="inlineStr">
         <is>
           <t>≥ 10</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E11" s="25" t="inlineStr">
         <is>
           <t>✅ Met</t>
         </is>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>Automated TCs</t>
         </is>
       </c>
-      <c r="B12" s="19" t="n">
+      <c r="B12" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="27" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D12" s="27" t="inlineStr">
         <is>
           <t>2–3</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr">
+      <c r="E12" s="27" t="inlineStr">
         <is>
           <t>✅ Met</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="28" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="B13" s="21" t="n">
+      <c r="B13" s="29" t="n">
         <v>15</v>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="29" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D13" s="21" t="inlineStr">
+      <c r="D13" s="29" t="inlineStr">
         <is>
           <t>≥ 80%</t>
         </is>
       </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="E13" s="29" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="22" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="B14" s="15" t="n">
+      <c r="B14" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D14" s="15" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>✅</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="22" t="inlineStr">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>Not Executed</t>
         </is>
       </c>
-      <c r="B15" s="23" t="n">
+      <c r="B15" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="31" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="28" t="inlineStr">
         <is>
           <t>Pass Rate</t>
         </is>
       </c>
-      <c r="B16" s="21" t="inlineStr">
+      <c r="B16" s="29" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C16" s="29" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D16" s="29" t="inlineStr">
         <is>
           <t>≥ 80%</t>
         </is>
       </c>
-      <c r="E16" s="21" t="inlineStr">
+      <c r="E16" s="29" t="inlineStr">
         <is>
           <t>✅ Met</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="32" t="inlineStr">
         <is>
           <t>🤖  AUTOMATION: 3 test cases automated using Playwright v1.45 (Chromium). All 9 smoke tests passed. See tests/ folder.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="25" t="inlineStr">
-        <is>
-          <t>💨  SMOKE TEST RESULTS (Playwright — Run on: 08 Jul 2026)</t>
+      <c r="A20" s="33" t="inlineStr">
+        <is>
+          <t>💨  SMOKE TEST RESULTS (Playwright — Run on: 14 Jul 2026)</t>
         </is>
       </c>
     </row>
@@ -1427,7 +2131,7 @@
       </c>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="26" t="inlineStr">
+      <c r="A22" s="34" t="inlineStr">
         <is>
           <t>S-001</t>
         </is>
@@ -1437,19 +2141,19 @@
           <t>Backend server responds on port 5000</t>
         </is>
       </c>
-      <c r="C22" s="27" t="inlineStr">
+      <c r="C22" s="35" t="inlineStr">
         <is>
           <t>407ms</t>
         </is>
       </c>
-      <c r="D22" s="28" t="inlineStr">
+      <c r="D22" s="36" t="inlineStr">
         <is>
           <t>✅ Pass</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="26" t="inlineStr">
+      <c r="A23" s="34" t="inlineStr">
         <is>
           <t>S-002</t>
         </is>
@@ -1459,19 +2163,19 @@
           <t>Health endpoint returns status:ok</t>
         </is>
       </c>
-      <c r="C23" s="27" t="inlineStr">
+      <c r="C23" s="35" t="inlineStr">
         <is>
           <t>348ms</t>
         </is>
       </c>
-      <c r="D23" s="28" t="inlineStr">
+      <c r="D23" s="36" t="inlineStr">
         <is>
           <t>✅ Pass</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="26" t="inlineStr">
+      <c r="A24" s="34" t="inlineStr">
         <is>
           <t>S-003</t>
         </is>
@@ -1481,19 +2185,19 @@
           <t>Dummy data is seeded (records exist)</t>
         </is>
       </c>
-      <c r="C24" s="27" t="inlineStr">
+      <c r="C24" s="35" t="inlineStr">
         <is>
           <t>387ms</t>
         </is>
       </c>
-      <c r="D24" s="28" t="inlineStr">
+      <c r="D24" s="36" t="inlineStr">
         <is>
           <t>✅ Pass</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="26" t="inlineStr">
+      <c r="A25" s="34" t="inlineStr">
         <is>
           <t>S-004</t>
         </is>
@@ -1503,41 +2207,41 @@
           <t>GET / returns HTTP 200 (dashboard served)</t>
         </is>
       </c>
-      <c r="C25" s="27" t="inlineStr">
+      <c r="C25" s="35" t="inlineStr">
         <is>
           <t>430ms</t>
         </is>
       </c>
-      <c r="D25" s="28" t="inlineStr">
+      <c r="D25" s="36" t="inlineStr">
         <is>
           <t>✅ Pass</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="26" t="inlineStr">
+      <c r="A26" s="34" t="inlineStr">
         <is>
           <t>S-005</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>GET /dummy/buses/live → 10 buses</t>
-        </is>
-      </c>
-      <c r="C26" s="27" t="inlineStr">
+          <t>GET /dummy/buses/live → 5 buses</t>
+        </is>
+      </c>
+      <c r="C26" s="35" t="inlineStr">
         <is>
           <t>323ms</t>
         </is>
       </c>
-      <c r="D26" s="28" t="inlineStr">
+      <c r="D26" s="36" t="inlineStr">
         <is>
           <t>✅ Pass</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="26" t="inlineStr">
+      <c r="A27" s="34" t="inlineStr">
         <is>
           <t>S-006</t>
         </is>
@@ -1547,19 +2251,19 @@
           <t>POST /telemetry → HTTP 201</t>
         </is>
       </c>
-      <c r="C27" s="27" t="inlineStr">
+      <c r="C27" s="35" t="inlineStr">
         <is>
           <t>445ms</t>
         </is>
       </c>
-      <c r="D27" s="28" t="inlineStr">
+      <c r="D27" s="36" t="inlineStr">
         <is>
           <t>✅ Pass</t>
         </is>
       </c>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="26" t="inlineStr">
+      <c r="A28" s="34" t="inlineStr">
         <is>
           <t>S-007</t>
         </is>
@@ -1569,19 +2273,19 @@
           <t>GET /dashboard.css served with correct MIME</t>
         </is>
       </c>
-      <c r="C28" s="27" t="inlineStr">
+      <c r="C28" s="35" t="inlineStr">
         <is>
           <t>338ms</t>
         </is>
       </c>
-      <c r="D28" s="28" t="inlineStr">
+      <c r="D28" s="36" t="inlineStr">
         <is>
           <t>✅ Pass</t>
         </is>
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="26" t="inlineStr">
+      <c r="A29" s="34" t="inlineStr">
         <is>
           <t>S-008</t>
         </is>
@@ -1591,19 +2295,19 @@
           <t>GET /dashboard.js served with correct MIME</t>
         </is>
       </c>
-      <c r="C29" s="27" t="inlineStr">
+      <c r="C29" s="35" t="inlineStr">
         <is>
           <t>325ms</t>
         </is>
       </c>
-      <c r="D29" s="28" t="inlineStr">
+      <c r="D29" s="36" t="inlineStr">
         <is>
           <t>✅ Pass</t>
         </is>
       </c>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="26" t="inlineStr">
+      <c r="A30" s="34" t="inlineStr">
         <is>
           <t>S-009</t>
         </is>
@@ -1613,12 +2317,12 @@
           <t>Dashboard page has no critical JS errors</t>
         </is>
       </c>
-      <c r="C30" s="27" t="inlineStr">
+      <c r="C30" s="35" t="inlineStr">
         <is>
           <t>8300ms</t>
         </is>
       </c>
-      <c r="D30" s="28" t="inlineStr">
+      <c r="D30" s="36" t="inlineStr">
         <is>
           <t>✅ Pass</t>
         </is>
